--- a/DRAGO/Junio/EXPENSAS-JUNIO.xlsx
+++ b/DRAGO/Junio/EXPENSAS-JUNIO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\DRAGO\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50EC47B9-2FAE-4833-B1AD-7FF6CDCBD2F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76EBEFB5-1610-4FB7-9DA8-82B7F2A991E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -280,9 +280,6 @@
     <t>Prevision ord</t>
   </si>
   <si>
-    <t>AUMENTADOS EN FEB 2025</t>
-  </si>
-  <si>
     <t>Expensas ordinarias</t>
   </si>
   <si>
@@ -292,9 +289,6 @@
     <t>Expensas 2do Vto</t>
   </si>
   <si>
-    <t>enzo habia pagado todo y lo pusimos con deuda</t>
-  </si>
-  <si>
     <t>Vto. 14/07</t>
   </si>
   <si>
@@ -302,6 +296,12 @@
   </si>
   <si>
     <t>Período JUNIO 2025</t>
+  </si>
+  <si>
+    <t>Valeria</t>
+  </si>
+  <si>
+    <t>AUMENTADOS EN JUNI 2025</t>
   </si>
 </sst>
 </file>
@@ -446,7 +446,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -483,12 +483,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="31">
     <border>
@@ -872,7 +866,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="140">
+  <cellXfs count="139">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1055,10 +1049,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="1" fillId="3" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="1" fillId="3" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1107,10 +1098,14 @@
     <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="16" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="11" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1516,10 +1511,10 @@
         <v>39</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1572,7 +1567,7 @@
       <c r="B17" s="87" t="s">
         <v>77</v>
       </c>
-      <c r="C17" s="99">
+      <c r="C17" s="84">
         <v>37561.17</v>
       </c>
       <c r="D17" s="5"/>
@@ -1583,7 +1578,7 @@
         <v>71</v>
       </c>
       <c r="B18" s="88"/>
-      <c r="C18" s="118">
+      <c r="C18" s="84">
         <v>3567.21</v>
       </c>
       <c r="D18" s="49"/>
@@ -1596,7 +1591,7 @@
       <c r="B19" s="89" t="s">
         <v>78</v>
       </c>
-      <c r="C19" s="99">
+      <c r="C19" s="84">
         <v>12654.47</v>
       </c>
       <c r="D19" s="5"/>
@@ -1610,7 +1605,7 @@
       <c r="B20" s="89" t="s">
         <v>78</v>
       </c>
-      <c r="C20" s="139">
+      <c r="C20" s="136">
         <v>154881.60999999999</v>
       </c>
       <c r="D20" s="49"/>
@@ -1623,21 +1618,21 @@
       <c r="B21" s="89" t="s">
         <v>76</v>
       </c>
-      <c r="C21" s="138">
-        <v>40180</v>
+      <c r="C21" s="84">
+        <v>44500</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="14"/>
       <c r="H21" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="90"/>
       <c r="B22" s="91"/>
-      <c r="C22" s="119">
+      <c r="C22" s="64">
         <f>SUM(C17:C21)</f>
-        <v>248844.46</v>
+        <v>253164.46</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -1645,16 +1640,16 @@
         <v>37</v>
       </c>
       <c r="B23" s="89"/>
-      <c r="C23" s="11"/>
+      <c r="C23" s="137"/>
     </row>
     <row r="24" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="77" t="s">
         <v>72</v>
       </c>
       <c r="B24" s="92" t="s">
-        <v>91</v>
-      </c>
-      <c r="C24" s="118">
+        <v>89</v>
+      </c>
+      <c r="C24" s="84">
         <f>65200+65200*5%</f>
         <v>68460</v>
       </c>
@@ -1692,7 +1687,7 @@
       <c r="B28" s="80"/>
       <c r="C28" s="93">
         <f>+C27+C22</f>
-        <v>317304.45999999996</v>
+        <v>321624.45999999996</v>
       </c>
       <c r="F28" s="22"/>
     </row>
@@ -1747,7 +1742,7 @@
       <c r="B37" s="35"/>
       <c r="C37" s="36">
         <f>+C35+C28</f>
-        <v>317304.45999999996</v>
+        <v>321624.45999999996</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -1761,7 +1756,7 @@
       </c>
       <c r="B40" s="34"/>
       <c r="C40" s="41">
-        <v>294321.9069224</v>
+        <v>260801.88812239992</v>
       </c>
       <c r="D40" s="6"/>
       <c r="E40" s="6"/>
@@ -1772,7 +1767,7 @@
       </c>
       <c r="C41" s="33">
         <f>'prorrateo '!F13</f>
-        <v>284928.3812</v>
+        <v>391672.39302100008</v>
       </c>
       <c r="D41" s="14"/>
       <c r="E41" s="14"/>
@@ -1791,7 +1786,7 @@
       </c>
       <c r="C43" s="94">
         <f>-(C28-C26)</f>
-        <v>-317304.45999999996</v>
+        <v>-321624.45999999996</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -1801,7 +1796,7 @@
       <c r="B44" s="34"/>
       <c r="C44" s="41">
         <f>SUM(C40:C43)</f>
-        <v>261945.82812239998</v>
+        <v>330849.82114340004</v>
       </c>
       <c r="D44" s="6"/>
     </row>
@@ -1904,7 +1899,7 @@
         <v>52</v>
       </c>
       <c r="E1" s="51">
-        <v>318448.40000000002</v>
+        <v>321624.45999999996</v>
       </c>
       <c r="G1" t="str">
         <f>'detalle y gastos'!C7</f>
@@ -1932,58 +1927,58 @@
       <c r="M2" s="103"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="124"/>
-      <c r="B3" s="122" t="s">
+      <c r="A3" s="121"/>
+      <c r="B3" s="119" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="130" t="s">
+      <c r="C3" s="127" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="131" t="s">
+      <c r="D3" s="128" t="s">
         <v>60</v>
       </c>
-      <c r="E3" s="122" t="s">
+      <c r="E3" s="119" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="128" t="s">
+      <c r="F3" s="125" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="130" t="s">
+      <c r="G3" s="127" t="s">
         <v>58</v>
       </c>
-      <c r="H3" s="128" t="s">
+      <c r="H3" s="125" t="s">
         <v>48</v>
       </c>
-      <c r="I3" s="130" t="s">
+      <c r="I3" s="127" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="132" t="s">
+      <c r="J3" s="129" t="s">
         <v>81</v>
       </c>
-      <c r="K3" s="126" t="s">
+      <c r="K3" s="123" t="s">
+        <v>84</v>
+      </c>
+      <c r="L3" s="123" t="s">
         <v>85</v>
       </c>
-      <c r="L3" s="126" t="s">
+      <c r="M3" s="123" t="s">
         <v>86</v>
       </c>
-      <c r="M3" s="126" t="s">
-        <v>87</v>
-      </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="125"/>
-      <c r="B4" s="123"/>
-      <c r="C4" s="130"/>
-      <c r="D4" s="131"/>
-      <c r="E4" s="123"/>
-      <c r="F4" s="129"/>
-      <c r="G4" s="130"/>
-      <c r="H4" s="129"/>
-      <c r="I4" s="130"/>
-      <c r="J4" s="132"/>
-      <c r="K4" s="127"/>
-      <c r="L4" s="127"/>
-      <c r="M4" s="127"/>
+      <c r="A4" s="122"/>
+      <c r="B4" s="120"/>
+      <c r="C4" s="127"/>
+      <c r="D4" s="128"/>
+      <c r="E4" s="120"/>
+      <c r="F4" s="126"/>
+      <c r="G4" s="127"/>
+      <c r="H4" s="126"/>
+      <c r="I4" s="127"/>
+      <c r="J4" s="129"/>
+      <c r="K4" s="124"/>
+      <c r="L4" s="124"/>
+      <c r="M4" s="124"/>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="104">
@@ -1999,11 +1994,11 @@
         <v>66</v>
       </c>
       <c r="E5" s="47">
-        <v>40540.144919999999</v>
-      </c>
-      <c r="F5" s="47">
+        <v>38532.256399999998</v>
+      </c>
+      <c r="F5" s="138">
         <f>E5</f>
-        <v>40540.144919999999</v>
+        <v>38532.256399999998</v>
       </c>
       <c r="G5" s="47">
         <f>E5-F5</f>
@@ -2019,15 +2014,15 @@
       <c r="J5" s="98"/>
       <c r="K5" s="111">
         <f>E1*I5</f>
-        <v>38532.256399999998</v>
+        <v>38916.559659999992</v>
       </c>
       <c r="L5" s="111">
         <f>E5-F5+H5+K5+J5</f>
-        <v>38532.256399999998</v>
+        <v>38916.559659999992</v>
       </c>
       <c r="M5" s="112">
         <f>L5+L5*4%</f>
-        <v>40073.546655999999</v>
+        <v>40473.222046399991</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
@@ -2044,18 +2039,19 @@
         <v>67</v>
       </c>
       <c r="E6" s="47">
-        <v>39673.982020000003</v>
-      </c>
-      <c r="F6" s="47">
-        <v>31231.37</v>
+        <v>47715.447421000004</v>
+      </c>
+      <c r="F6" s="138">
+        <f>E6</f>
+        <v>47715.447421000004</v>
       </c>
       <c r="G6" s="47">
         <f t="shared" ref="G6:G12" si="0">E6-F6</f>
-        <v>8442.6120200000041</v>
+        <v>0</v>
       </c>
       <c r="H6" s="47">
         <f t="shared" ref="H6:H12" si="1">IF(G6&gt;0,G6*5%,0)</f>
-        <v>422.13060100000024</v>
+        <v>0</v>
       </c>
       <c r="I6" s="110">
         <v>0.122</v>
@@ -2063,20 +2059,18 @@
       <c r="J6" s="98"/>
       <c r="K6" s="111">
         <f>E1*I6</f>
-        <v>38850.7048</v>
+        <v>39238.184119999998</v>
       </c>
       <c r="L6" s="111">
         <f t="shared" ref="L6:L12" si="2">E6-F6+H6+K6+J6</f>
-        <v>47715.447421000004</v>
+        <v>39238.184119999998</v>
       </c>
       <c r="M6" s="112">
         <f t="shared" ref="M6:M12" si="3">L6+L6*4%</f>
-        <v>49624.065317840003</v>
-      </c>
-      <c r="O6" s="121" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q6" s="120"/>
+        <v>40807.711484799998</v>
+      </c>
+      <c r="O6" s="135"/>
+      <c r="Q6" s="118"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="104">
@@ -2088,13 +2082,15 @@
       <c r="C7" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="62"/>
+      <c r="D7" s="62" t="s">
+        <v>90</v>
+      </c>
       <c r="E7" s="47">
-        <v>39199.974840000003</v>
-      </c>
-      <c r="F7" s="47">
+        <v>37258.462800000008</v>
+      </c>
+      <c r="F7" s="138">
         <f>E7</f>
-        <v>39199.974840000003</v>
+        <v>37258.462800000008</v>
       </c>
       <c r="G7" s="47">
         <f t="shared" si="0"/>
@@ -2110,15 +2106,15 @@
       <c r="J7" s="98"/>
       <c r="K7" s="111">
         <f>E1*I7</f>
-        <v>37258.462800000008</v>
+        <v>37630.061819999995</v>
       </c>
       <c r="L7" s="111">
         <f t="shared" si="2"/>
-        <v>37258.462800000008</v>
+        <v>37630.061819999995</v>
       </c>
       <c r="M7" s="112">
         <f t="shared" si="3"/>
-        <v>38748.801312000011</v>
+        <v>39135.264292799999</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
@@ -2135,16 +2131,18 @@
         <v>62</v>
       </c>
       <c r="E8" s="47">
-        <v>122096.58983218967</v>
-      </c>
-      <c r="F8" s="47"/>
+        <v>165459.88212379918</v>
+      </c>
+      <c r="F8" s="138">
+        <v>100000</v>
+      </c>
       <c r="G8" s="47">
         <f t="shared" si="0"/>
-        <v>122096.58983218967</v>
+        <v>65459.88212379918</v>
       </c>
       <c r="H8" s="47">
         <f t="shared" si="1"/>
-        <v>6104.8294916094837</v>
+        <v>3272.994106189959</v>
       </c>
       <c r="I8" s="110">
         <v>0.11700000000000001</v>
@@ -2152,15 +2150,15 @@
       <c r="J8" s="98"/>
       <c r="K8" s="111">
         <f>E1*I8</f>
-        <v>37258.462800000008</v>
+        <v>37630.061819999995</v>
       </c>
       <c r="L8" s="111">
         <f t="shared" si="2"/>
-        <v>165459.88212379918</v>
+        <v>106362.93804998914</v>
       </c>
       <c r="M8" s="112">
         <f t="shared" si="3"/>
-        <v>172078.27740875114</v>
+        <v>110617.45557198871</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -2177,11 +2175,11 @@
         <v>65</v>
       </c>
       <c r="E9" s="47">
-        <v>45900.825240000006</v>
-      </c>
-      <c r="F9" s="47">
+        <v>43627.430800000009</v>
+      </c>
+      <c r="F9" s="138">
         <f t="shared" ref="F9" si="4">E9</f>
-        <v>45900.825240000006</v>
+        <v>43627.430800000009</v>
       </c>
       <c r="G9" s="47">
         <f t="shared" si="0"/>
@@ -2197,15 +2195,15 @@
       <c r="J9" s="98"/>
       <c r="K9" s="111">
         <f>E1*I9</f>
-        <v>43627.430800000009</v>
+        <v>44062.551019999999</v>
       </c>
       <c r="L9" s="111">
         <f t="shared" si="2"/>
-        <v>43627.430800000009</v>
+        <v>44062.551019999999</v>
       </c>
       <c r="M9" s="112">
         <f t="shared" si="3"/>
-        <v>45372.528032000009</v>
+        <v>45825.053060799997</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -2222,11 +2220,11 @@
         <v>64</v>
       </c>
       <c r="E10" s="47">
-        <v>42955.266120000015</v>
-      </c>
-      <c r="F10" s="47">
+        <v>42035.188800000004</v>
+      </c>
+      <c r="F10" s="138">
         <f>E10</f>
-        <v>42955.266120000015</v>
+        <v>42035.188800000004</v>
       </c>
       <c r="G10" s="47">
         <f t="shared" si="0"/>
@@ -2242,15 +2240,15 @@
       <c r="J10" s="98"/>
       <c r="K10" s="111">
         <f>E1*I10</f>
-        <v>42035.188800000004</v>
+        <v>42454.428719999996</v>
       </c>
       <c r="L10" s="111">
         <f t="shared" si="2"/>
-        <v>42035.188800000004</v>
+        <v>42454.428719999996</v>
       </c>
       <c r="M10" s="112">
         <f t="shared" si="3"/>
-        <v>43716.596352</v>
+        <v>44152.605868799998</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
@@ -2267,11 +2265,11 @@
         <v>63</v>
       </c>
       <c r="E11" s="47">
-        <v>42550.40004</v>
-      </c>
-      <c r="F11" s="47">
+        <v>40442.946800000005</v>
+      </c>
+      <c r="F11" s="138">
         <f>E11</f>
-        <v>42550.40004</v>
+        <v>40442.946800000005</v>
       </c>
       <c r="G11" s="47">
         <f t="shared" si="0"/>
@@ -2287,15 +2285,15 @@
       <c r="J11" s="98"/>
       <c r="K11" s="111">
         <f>E1*I11</f>
-        <v>40442.946800000005</v>
+        <v>40846.306419999994</v>
       </c>
       <c r="L11" s="111">
         <f t="shared" si="2"/>
-        <v>40442.946800000005</v>
+        <v>40846.306419999994</v>
       </c>
       <c r="M11" s="112">
         <f t="shared" si="3"/>
-        <v>42060.664672000006</v>
+        <v>42480.158676799991</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
@@ -2312,15 +2310,14 @@
         <v>61</v>
       </c>
       <c r="E12" s="47">
-        <v>42550.40004</v>
-      </c>
-      <c r="F12" s="47">
-        <f>E12</f>
-        <v>42550.40004</v>
+        <v>40442.946800000005</v>
+      </c>
+      <c r="F12" s="138">
+        <v>42060.66</v>
       </c>
       <c r="G12" s="47">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-1617.7131999999983</v>
       </c>
       <c r="H12" s="47">
         <f t="shared" si="1"/>
@@ -2332,15 +2329,15 @@
       <c r="J12" s="98"/>
       <c r="K12" s="111">
         <f>E1*I12</f>
-        <v>40442.946800000005</v>
+        <v>40846.306419999994</v>
       </c>
       <c r="L12" s="111">
         <f t="shared" si="2"/>
-        <v>40442.946800000005</v>
+        <v>39228.593219999995</v>
       </c>
       <c r="M12" s="112">
         <f t="shared" si="3"/>
-        <v>42060.664672000006</v>
+        <v>40797.736948799997</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2352,16 +2349,16 @@
       <c r="D13" s="115"/>
       <c r="E13" s="116">
         <f>SUM(E5:E12)</f>
-        <v>415467.58305218967</v>
+        <v>455514.56194479926</v>
       </c>
       <c r="F13" s="105">
         <f>SUM(F5:F12)</f>
-        <v>284928.3812</v>
+        <v>391672.39302100008</v>
       </c>
       <c r="G13" s="105"/>
       <c r="H13" s="105">
         <f>SUM(H5:H12)</f>
-        <v>6526.9600926094836</v>
+        <v>3272.994106189959</v>
       </c>
       <c r="I13" s="106">
         <f t="shared" ref="I13" si="5">SUM(I5:I12)</f>
@@ -2373,15 +2370,15 @@
       </c>
       <c r="K13" s="116">
         <f>SUM(K5:K12)</f>
-        <v>318448.40000000002</v>
+        <v>321624.45999999996</v>
       </c>
       <c r="L13" s="116">
         <f>SUM(L5:L12)</f>
-        <v>455514.56194479926</v>
+        <v>388739.62302998907</v>
       </c>
       <c r="M13" s="117">
         <f>SUM(M5:M12)</f>
-        <v>473735.14442259114</v>
+        <v>404289.20795118867</v>
       </c>
     </row>
     <row r="16" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
@@ -2832,11 +2829,11 @@
       <c r="D1" s="58">
         <v>50000</v>
       </c>
-      <c r="H1" s="137">
+      <c r="H1" s="134">
         <v>250000</v>
       </c>
-      <c r="I1" s="137"/>
-      <c r="J1" s="137"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="55" t="s">
@@ -2900,13 +2897,13 @@
         <v>58</v>
       </c>
       <c r="K4" s="71"/>
-      <c r="L4" s="135" t="s">
+      <c r="L4" s="132" t="s">
         <v>74</v>
       </c>
       <c r="M4" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="N4" s="133" t="s">
+      <c r="N4" s="130" t="s">
         <v>59</v>
       </c>
       <c r="P4" s="21"/>
@@ -2935,11 +2932,11 @@
         <v>73</v>
       </c>
       <c r="K5" s="61"/>
-      <c r="L5" s="136"/>
+      <c r="L5" s="133"/>
       <c r="M5" s="82" t="s">
         <v>75</v>
       </c>
-      <c r="N5" s="134"/>
+      <c r="N5" s="131"/>
       <c r="P5" s="21"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
